--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-documentreference.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-documentreference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-documentreference.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-documentreference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-documentreference.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-documentreference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-documentreference.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-documentreference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -281,7 +281,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -394,7 +394,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>DocumentReference.meta.versionId</t>
@@ -709,7 +709,7 @@
     <t>DocumentReference.status</t>
   </si>
   <si>
-    <t>電流|スーパー付き|エラーに入った / current | superseded | entered-in-error</t>
+    <t>電流|スーパー付き|エラー入力 / current | superseded | entered-in-error</t>
   </si>
   <si>
     <t>このドキュメント参照のステータス。 / The status of this document reference.</t>
@@ -747,7 +747,7 @@
     <t>DocumentReference.docStatus</t>
   </si>
   <si>
-    <t>予備|ファイナル|修正|エラーに入った / preliminary | final | amended | entered-in-error</t>
+    <t>予備|ファイナル|修正|エラー入力 / preliminary | final | amended | entered-in-error</t>
   </si>
   <si>
     <t>基礎となる文書のステータス。 / The status of the underlying document.</t>
@@ -778,7 +778,7 @@
 </t>
   </si>
   <si>
-    <t>ドキュメントの種類（可能であれば泡） / Kind of document (LOINC if possible)</t>
+    <t>ドキュメントの種類（可能であればLoinc） / Kind of document (LOINC if possible)</t>
   </si>
   <si>
     <t>参照されている特定の種類のドキュメントを指定します（例：履歴と物理的、排出概要、進行状況ノート）。これは通常、文書を参照する目的に相当します。 / Specifies the particular kind of document referenced  (e.g. History and Physical, Discharge Summary, Progress Note). This usually equates to the purpose of making the document referenced.</t>
@@ -1282,7 +1282,7 @@
     <t>ドキュメントコンテンツのコンテキスト / Context of the document  content</t>
   </si>
   <si>
-    <t>ドキュメントコンテンツが関連付けられている臨床的遭遇またはケアの種類について説明します。 / Describes the clinical encounter or type of care that the document content is associated with.</t>
+    <t>ドキュメントコンテンツが関連付けられている臨床的Enounterまたはケアの種類について説明します。 / Describes the clinical encounter or type of care that the document content is associated with.</t>
   </si>
   <si>
     <t>Event.context</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-documentreference.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-documentreference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-release</t>
+    <t>1.2.0-b</t>
   </si>
   <si>
     <t>Name</t>
